--- a/spec/files/properties/type_location_blank_error.xlsx
+++ b/spec/files/properties/type_location_blank_error.xlsx
@@ -26,7 +26,7 @@
     <t xml:space="preserve">tipo-propiedad</t>
   </si>
   <si>
-    <t xml:space="preserve">localización</t>
+    <t xml:space="preserve">localizacion</t>
   </si>
   <si>
     <t xml:space="preserve">Propio#pro-own</t>
